--- a/docs/archive/技能规范化（v3）.xlsx
+++ b/docs/archive/技能规范化（v3）.xlsx
@@ -1,13 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\刘胤轩\WPSDrive\563952371_1\WPS云盘\小说\游戏\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7590"/>
+    <workbookView windowWidth="28800" windowHeight="11520" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="516">
   <si>
     <t>技能名字</t>
   </si>
@@ -6244,6 +6250,738 @@
   </si>
   <si>
     <t>锁定技，开局声明，当场上玩家触发隐性技能效果时，使该技能暴露</t>
+  </si>
+  <si>
+    <t>序号</t>
+  </si>
+  <si>
+    <t>融合素材</t>
+  </si>
+  <si>
+    <t>原效果</t>
+  </si>
+  <si>
+    <t>融合效果</t>
+  </si>
+  <si>
+    <t>使用时机</t>
+  </si>
+  <si>
+    <t>目标选取</t>
+  </si>
+  <si>
+    <t>技能标签</t>
+  </si>
+  <si>
+    <t>冰火两仪眼</t>
+  </si>
+  <si>
+    <t>火烧大地+霜落大地</t>
+  </si>
+  <si>
+    <t>失去</t>
+  </si>
+  <si>
+    <t>冰火两仪眼：限2次，你加4血，除你外所有玩家受到1点冰火系伤害，消除其他玩家持有的冰系和火系技能，被消除技能的玩家受到伤害+1</t>
+  </si>
+  <si>
+    <t>随时</t>
+  </si>
+  <si>
+    <t>无需选取</t>
+  </si>
+  <si>
+    <t>冰系技能，火系技能</t>
+  </si>
+  <si>
+    <t>交流电</t>
+  </si>
+  <si>
+    <t>雷电法术+电击法术</t>
+  </si>
+  <si>
+    <t>增加次数</t>
+  </si>
+  <si>
+    <t>电击法术增加到2次</t>
+  </si>
+  <si>
+    <t>烽火赤壁</t>
+  </si>
+  <si>
+    <t>火烧大地+净化之风</t>
+  </si>
+  <si>
+    <t>强化</t>
+  </si>
+  <si>
+    <t>火烧大地增加到3次，净化之风强化：扣血不再判断奇偶，每次使用净化之风，除你外所有玩家均会受到2次1点法术伤害</t>
+  </si>
+  <si>
+    <t>杀级换</t>
+  </si>
+  <si>
+    <t>杀换+级换</t>
+  </si>
+  <si>
+    <t>杀换强化：不再耗饼，级换强化：可将攻击，等级，耗饼数相互交换</t>
+  </si>
+  <si>
+    <t>虚幻</t>
+  </si>
+  <si>
+    <t>换防+幻防</t>
+  </si>
+  <si>
+    <t>虚幻：消耗1饼，切换小防和油条或油条和石头</t>
+  </si>
+  <si>
+    <t>幻境双罩</t>
+  </si>
+  <si>
+    <t>神罩+鬼罩</t>
+  </si>
+  <si>
+    <t>神罩、鬼罩各增加到5次</t>
+  </si>
+  <si>
+    <t>冰火狂暴曲</t>
+  </si>
+  <si>
+    <t>熔岩之怒+凛冬之怒</t>
+  </si>
+  <si>
+    <t>冰火狂暴曲：你每出3次小防/油条/石头，获得1层“冰火”印记，最高3层；变招阶段，当你使用攻击时，可以消耗x层，使该攻击变为冰火系，攻击+x，等级+x，命中后赋予x回合“冰冻”；冰冻：无法出招；</t>
+  </si>
+  <si>
+    <t>被动效果；印记使用：变招阶段</t>
+  </si>
+  <si>
+    <t>自身本回合使用的攻击</t>
+  </si>
+  <si>
+    <t>生死符</t>
+  </si>
+  <si>
+    <t>毒箭雨+冰箭雨</t>
+  </si>
+  <si>
+    <t>保留</t>
+  </si>
+  <si>
+    <t>生死符：你的万箭齐发破弹</t>
+  </si>
+  <si>
+    <t>冰系技能，毒系技能</t>
+  </si>
+  <si>
+    <t>雷霆之心</t>
+  </si>
+  <si>
+    <t>三千雷动+大地之心</t>
+  </si>
+  <si>
+    <t>大地之心强化：+4防御值变更为+4血量；三千雷动强化：三千雷动的目标包括玩家自己</t>
+  </si>
+  <si>
+    <t>极寒风暴</t>
+  </si>
+  <si>
+    <t>暴风雪+狂风骤雪</t>
+  </si>
+  <si>
+    <t>狂风骤雪强化：攻击变为2+2</t>
+  </si>
+  <si>
+    <t>逆转星移</t>
+  </si>
+  <si>
+    <t>逆转+斗转星移</t>
+  </si>
+  <si>
+    <t>斗转星移强化：可转移不超过无限的伤害</t>
+  </si>
+  <si>
+    <t>破天圣剑</t>
+  </si>
+  <si>
+    <t>青釭剑+双刃剑</t>
+  </si>
+  <si>
+    <t>青釭剑强化：你的攻击无视换防、幻防、八卦阵、藤甲、无形之盾、神之庇佑、不死金身、后盾、神罩、鬼罩、闪现、金钟罩；双刃剑强化：你可以-2血破弹</t>
+  </si>
+  <si>
+    <t>神域之种</t>
+  </si>
+  <si>
+    <t>神之庇护+神族水晶</t>
+  </si>
+  <si>
+    <t>神之庇佑强化：每轮前3回合无敌；神族水晶强化：出招的最终等级+2</t>
+  </si>
+  <si>
+    <t>毁灭之盾</t>
+  </si>
+  <si>
+    <t>全力一击+后盾</t>
+  </si>
+  <si>
+    <t>全力一击强化：全力一击变成0级，反噬减少为-1血</t>
+  </si>
+  <si>
+    <t>神之子</t>
+  </si>
+  <si>
+    <t>天佑之魂+沐浴圣光</t>
+  </si>
+  <si>
+    <t>天佑之魂强化：对血量取绝对值后，先×3，然后+6</t>
+  </si>
+  <si>
+    <t>魔域</t>
+  </si>
+  <si>
+    <t>圣域+邪域</t>
+  </si>
+  <si>
+    <t>魔域：第3x轮轮末，选取3个可重复的目标，各吸取1血</t>
+  </si>
+  <si>
+    <t>被动效果</t>
+  </si>
+  <si>
+    <t>回合末阶段，选取3个可重复的目标</t>
+  </si>
+  <si>
+    <t>暗影狙击</t>
+  </si>
+  <si>
+    <t>古淀刀+狙击枪</t>
+  </si>
+  <si>
+    <t>暗影狙击：你补刀且目标饼为0时，目标退游</t>
+  </si>
+  <si>
+    <t>灵魂修复</t>
+  </si>
+  <si>
+    <t>创伤聚合+治愈术</t>
+  </si>
+  <si>
+    <t>灵魂修复：当你受到伤害后，1轮后血量回复为满血，该轮轮初+1饼</t>
+  </si>
+  <si>
+    <t>暗影战斧</t>
+  </si>
+  <si>
+    <t>死神之镰+邪域</t>
+  </si>
+  <si>
+    <t>暗影战斧：他人受到x点伤害时，你加x/4（下取整）血</t>
+  </si>
+  <si>
+    <t>泣血之刃</t>
+  </si>
+  <si>
+    <t>嗜血+复仇之刃</t>
+  </si>
+  <si>
+    <t>嗜血强化：当你的攻击造成x点伤害时，你+x/2（下取整）点生命；复仇之刃强化：完成4次复仇即可胜利</t>
+  </si>
+  <si>
+    <t>末世</t>
+  </si>
+  <si>
+    <t>嗜血+毁灭之力</t>
+  </si>
+  <si>
+    <t>嗜血强化：当你的攻击造成x点伤害时，你+x/2（下取整）点生命；毁灭之力强化：冷却时间降低为1轮1次</t>
+  </si>
+  <si>
+    <t>制裁之刃</t>
+  </si>
+  <si>
+    <t>嗜血+血之哀</t>
+  </si>
+  <si>
+    <t>制裁之刃：全场加血归你，你无视血之哀</t>
+  </si>
+  <si>
+    <t>枯萎</t>
+  </si>
+  <si>
+    <t>血之哀+衰竭</t>
+  </si>
+  <si>
+    <t>枯萎：额外选择1个正整数加入衰竭效果</t>
+  </si>
+  <si>
+    <t>开局阶段，输入一个正整数</t>
+  </si>
+  <si>
+    <t>沙皇</t>
+  </si>
+  <si>
+    <t>沙子+沙子</t>
+  </si>
+  <si>
+    <t>沙皇：变换为一个自选小技能和一个自选二融合，使用时需声明为沙子变化。若场上有其他玩家持有该技能，你本次变换失败，你退游</t>
+  </si>
+  <si>
+    <t>下拉列表中选取小技能和二融合</t>
+  </si>
+  <si>
+    <t>空城计</t>
+  </si>
+  <si>
+    <t>空+遗计</t>
+  </si>
+  <si>
+    <t>遗计强化：+2饼变为+3饼；空城计：每轮前2回合绝对无敌</t>
+  </si>
+  <si>
+    <t>空之轨迹</t>
+  </si>
+  <si>
+    <t>闪现+过往时空</t>
+  </si>
+  <si>
+    <t>闪现强化：冷却时间降低为2轮1次；过往时空强化：拆分为2次，每次暂时退游3轮</t>
+  </si>
+  <si>
+    <t>虚无</t>
+  </si>
+  <si>
+    <t>空+闪现</t>
+  </si>
+  <si>
+    <t>闪现强化：冷却时间降低为1轮1次</t>
+  </si>
+  <si>
+    <t>后羿•七日连珠</t>
+  </si>
+  <si>
+    <t>日+连爆</t>
+  </si>
+  <si>
+    <t>日强化：日享有连爆效果（命中后获得免费日机会）</t>
+  </si>
+  <si>
+    <t>弹力球</t>
+  </si>
+  <si>
+    <t>绝弹+散弹</t>
+  </si>
+  <si>
+    <t>弹力球：你的反弹无视破弹</t>
+  </si>
+  <si>
+    <t>根源之目</t>
+  </si>
+  <si>
+    <t>烈弓+火眼金睛</t>
+  </si>
+  <si>
+    <t>根源之目：你无视弹力球</t>
+  </si>
+  <si>
+    <t>斗战胜佛</t>
+  </si>
+  <si>
+    <t>齐天大圣+火眼金睛</t>
+  </si>
+  <si>
+    <t>金箍棒：技能攻击，3饼，攻无限，3级，任意防</t>
+  </si>
+  <si>
+    <t>技能攻击</t>
+  </si>
+  <si>
+    <t>单体</t>
+  </si>
+  <si>
+    <t>圣灵觉醒</t>
+  </si>
+  <si>
+    <t>圣+齐天大圣</t>
+  </si>
+  <si>
+    <t>圣灵觉醒：技能出招，x饼，+4x饼，出圣且受到攻击伤害时，直接变为0血，已经0血时该效果不触发</t>
+  </si>
+  <si>
+    <t>技能出招</t>
+  </si>
+  <si>
+    <t>六芒星阵</t>
+  </si>
+  <si>
+    <t>六芒星+八卦阵</t>
+  </si>
+  <si>
+    <t>八卦阵强化：受到攻击伤害-2；六芒星阵：你受到攻击时，1/6无敌，1/12触发六芒星效果，1/12反弹该攻击</t>
+  </si>
+  <si>
+    <t>自然之灵</t>
+  </si>
+  <si>
+    <t>藤甲+森林的低吟</t>
+  </si>
+  <si>
+    <t>自然之灵：你免疫火系技能</t>
+  </si>
+  <si>
+    <t>帝灵之境</t>
+  </si>
+  <si>
+    <t>帝炎之境+圣灵之境</t>
+  </si>
+  <si>
+    <t>帝灵之境：你免疫法伤，受到法伤时发出者受到1点火系法伤</t>
+  </si>
+  <si>
+    <t>阳光之夜</t>
+  </si>
+  <si>
+    <t>阳光普照+永远之夜</t>
+  </si>
+  <si>
+    <t>阳光普照、永远之夜强化：效果收束到自己身边（即阳光普照和永远之夜只对自己发出的和自己受到的攻击生效）</t>
+  </si>
+  <si>
+    <t>阳炎之怒</t>
+  </si>
+  <si>
+    <t>阳光普照+熔岩之怒</t>
+  </si>
+  <si>
+    <t>熔岩之怒强化：变为+2、+2，出石头、油条均可获得“熔岩”印记</t>
+  </si>
+  <si>
+    <t>野蛮人</t>
+  </si>
+  <si>
+    <t>逆转+文明人</t>
+  </si>
+  <si>
+    <t>逆转增加到2次；野蛮人：场上有人说脏话时，他-1血，不重开，全场文明人无法加血</t>
+  </si>
+  <si>
+    <t>破军</t>
+  </si>
+  <si>
+    <t>双刃剑+乱舞</t>
+  </si>
+  <si>
+    <t>双刃剑强化：-1血可群破防；破军：你的攻击对血量不低于初始血量1/2的目标造成伤害+1</t>
+  </si>
+  <si>
+    <t>无尽战刃</t>
+  </si>
+  <si>
+    <t>青釭剑+古淀刀</t>
+  </si>
+  <si>
+    <t>无尽战刃：你造成的攻击伤害有1/2概率翻倍</t>
+  </si>
+  <si>
+    <t>反伤刺甲</t>
+  </si>
+  <si>
+    <t>藤甲+帝炎之境</t>
+  </si>
+  <si>
+    <t>失去帝炎之境，保留藤甲</t>
+  </si>
+  <si>
+    <t>藤甲强化：受到火系伤害时不再受到额外伤害；反伤刺甲：有人对你造成x点伤害时，他受到x/2（上取整）点法伤</t>
+  </si>
+  <si>
+    <t>贤者之书</t>
+  </si>
+  <si>
+    <t>文明人+卷子</t>
+  </si>
+  <si>
+    <t>文明人强化：变为+2血</t>
+  </si>
+  <si>
+    <t>博学者之怒</t>
+  </si>
+  <si>
+    <t>森林的低吟+邪域</t>
+  </si>
+  <si>
+    <t>博学者之怒：你的所有法术伤害×2，森林的低吟回血×2</t>
+  </si>
+  <si>
+    <t>冰霜长矛</t>
+  </si>
+  <si>
+    <t>霜落大地+寒冰剑</t>
+  </si>
+  <si>
+    <t>霜落大地强化：变为+8/+2；寒冰剑强化：不需要不造成伤害</t>
+  </si>
+  <si>
+    <t>电闪雷鸣</t>
+  </si>
+  <si>
+    <t>闪电护体+鬼道</t>
+  </si>
+  <si>
+    <t>电闪雷鸣：闪电护体每免疫1个攻击，加1次鬼道</t>
+  </si>
+  <si>
+    <t>风语之森</t>
+  </si>
+  <si>
+    <t>净化之风+森林的低吟</t>
+  </si>
+  <si>
+    <t>净化之风强化：扣血不再判断奇偶，每次使用净化之风，除你外所有玩家均会受到1点法术伤害</t>
+  </si>
+  <si>
+    <t>神隐双莲</t>
+  </si>
+  <si>
+    <t>神隐红莲+神隐青莲</t>
+  </si>
+  <si>
+    <t>神隐双莲：当你濒死时，+3血，下轮初额外+1饼</t>
+  </si>
+  <si>
+    <t>红莲斗篷</t>
+  </si>
+  <si>
+    <t>神隐红莲+暗影盾</t>
+  </si>
+  <si>
+    <t>暗影盾强化：+10防御值；神隐红莲强化：每触发1次神隐红莲，对全场释放1次火烧大地</t>
+  </si>
+  <si>
+    <t>血魔之怒</t>
+  </si>
+  <si>
+    <t>凝血之力+血水屏障</t>
+  </si>
+  <si>
+    <t>血水屏障强化：变为+6防御值；凝血之力强化：加饼不再有上限</t>
+  </si>
+  <si>
+    <t>名刀司命</t>
+  </si>
+  <si>
+    <t>神之庇护+不死金身</t>
+  </si>
+  <si>
+    <t>名刀司命：当你濒死时，只有3至5回合可受到致死攻击伤害</t>
+  </si>
+  <si>
+    <t>天火之狱</t>
+  </si>
+  <si>
+    <t>浴火重生+地狱使徒</t>
+  </si>
+  <si>
+    <t>浴火重生强化：耗饼减少为3；地狱使徒强化：对自己使用时保留技能</t>
+  </si>
+  <si>
+    <t>神界炼魂</t>
+  </si>
+  <si>
+    <t>百炼成神+神族水晶</t>
+  </si>
+  <si>
+    <t>百炼成神强化：攻击20次即可胜利；神族水晶强化：+2等级</t>
+  </si>
+  <si>
+    <t>山崩地裂</t>
+  </si>
+  <si>
+    <t>碎石掌+裂山拳</t>
+  </si>
+  <si>
+    <t>山崩地裂：技能攻击，3饼，攻5，5级，饼防，对石头退游</t>
+  </si>
+  <si>
+    <t>宗师之力</t>
+  </si>
+  <si>
+    <t>破地之力+毁灭之力</t>
+  </si>
+  <si>
+    <t>毁灭之力强化：毁灭之力冷却时间减少到1轮1次，使用毁灭之力时你无视破地之力</t>
+  </si>
+  <si>
+    <t>贤者的庇护</t>
+  </si>
+  <si>
+    <t>神之庇佑+文明人</t>
+  </si>
+  <si>
+    <t>文明人强化：变为+2血；贤者的庇护：限1次，复活阶段可用，2血复活</t>
+  </si>
+  <si>
+    <t>绝对天盾</t>
+  </si>
+  <si>
+    <t>绝对值+绝对守护</t>
+  </si>
+  <si>
+    <t>绝对守护强化：耗饼减少为x/3，可将群攻变为指向天的单体攻击</t>
+  </si>
+  <si>
+    <t>神域守护</t>
+  </si>
+  <si>
+    <t>绝对守护+十字守护</t>
+  </si>
+  <si>
+    <t>绝对守护强化：耗饼变为x/4；十字守护强化：2变为3</t>
+  </si>
+  <si>
+    <t>不死鸟之眼</t>
+  </si>
+  <si>
+    <t>浴火重生+创伤聚合</t>
+  </si>
+  <si>
+    <t>不死鸟之眼：所有加血×2</t>
+  </si>
+  <si>
+    <t>霸者重装</t>
+  </si>
+  <si>
+    <t>圣域+创伤聚合</t>
+  </si>
+  <si>
+    <t>圣域强化：1轮1次；创伤聚合强化：增加至加4血</t>
+  </si>
+  <si>
+    <t>辉月</t>
+  </si>
+  <si>
+    <t>神之庇护+闪现</t>
+  </si>
+  <si>
+    <t>失去闪现，保留神之庇护</t>
+  </si>
+  <si>
+    <t>辉月：控制技，2轮限1次，2回合无敌，不能出招</t>
+  </si>
+  <si>
+    <t>猥琐小叔叔</t>
+  </si>
+  <si>
+    <t>撸日丁抠4选2</t>
+  </si>
+  <si>
+    <t>猥琐小叔叔：选择4个技能中的1个获得，不可融合成猥琐大叔叔</t>
+  </si>
+  <si>
+    <t>下拉列表显示撸、日、丁、抠</t>
+  </si>
+  <si>
+    <t>黑白板</t>
+  </si>
+  <si>
+    <t>黑板+白板</t>
+  </si>
+  <si>
+    <t>黑白板：场上剩余人数不多于3时，你胜利</t>
+  </si>
+  <si>
+    <t>逐日之弓</t>
+  </si>
+  <si>
+    <t>顺手牵羊+普天同庆</t>
+  </si>
+  <si>
+    <t>普天同庆强化：可命中最远的玩家；顺手牵羊强化：可获知全场玩家各1个技能并获得其中2个</t>
+  </si>
+  <si>
+    <t>水火双生</t>
+  </si>
+  <si>
+    <t>火焰刀+寒冰剑</t>
+  </si>
+  <si>
+    <t>寒冰剑强化：不需要不造成伤害；火焰刀强化：你的杀变为3/3，冰火系</t>
+  </si>
+  <si>
+    <t>冰火双漩</t>
+  </si>
+  <si>
+    <t>冰漩决+火漩决</t>
+  </si>
+  <si>
+    <t>冰火双漩：技能攻击，3饼，攻4，3级，冰火系，石头防，可对连续的1至3人使用，命中冰冻2回合</t>
+  </si>
+  <si>
+    <t>连续的1到3名玩家</t>
+  </si>
+  <si>
+    <t>魔女斗篷</t>
+  </si>
+  <si>
+    <t>暗影盾+血水屏障</t>
+  </si>
+  <si>
+    <t>暗影盾强化：+10防御值；血水屏障强化：+6防御值</t>
+  </si>
+  <si>
+    <t>大抠天下</t>
+  </si>
+  <si>
+    <t>抠+普天同庆</t>
+  </si>
+  <si>
+    <t>抠强化：不再会被弹；普天同庆强化：可攻击最远的玩家</t>
+  </si>
+  <si>
+    <t>回响之杖</t>
+  </si>
+  <si>
+    <t>火球+乱舞</t>
+  </si>
+  <si>
+    <t>火球强化：溅射变为4/2/1，溅射均石头防</t>
+  </si>
+  <si>
+    <t>天魔舞</t>
+  </si>
+  <si>
+    <t>镜像法术+乱舞</t>
+  </si>
+  <si>
+    <t>镜像法术强化：可以镜像一个二融合和一个小技能</t>
+  </si>
+  <si>
+    <t>永夜之刃</t>
+  </si>
+  <si>
+    <t>永远之夜+复仇之刃</t>
+  </si>
+  <si>
+    <t>复仇之刃强化：你的攻击打在永夜上也计算复仇次数</t>
+  </si>
+  <si>
+    <t>纯净苍穹</t>
+  </si>
+  <si>
+    <t>绝对守护+幻防</t>
+  </si>
+  <si>
+    <t>纯净苍穹：你使用耗饼的控制技时，本回合免疫不良</t>
+  </si>
+  <si>
+    <t>核战</t>
+  </si>
+  <si>
+    <t>核反应堆+普天同庆</t>
+  </si>
+  <si>
+    <t>普天同庆强化：可攻击最远的玩家；核战：全场玩家核爆/超核爆耗饼-3，你-5</t>
   </si>
 </sst>
 </file>
@@ -6265,13 +7003,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -6899,18 +7637,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -7442,31 +8183,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G121"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="8.72727272727273" style="1"/>
-    <col min="2" max="2" width="11.0909090909091" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.725" style="1"/>
+    <col min="2" max="2" width="11.0916666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="21" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6363636363636" style="1" customWidth="1"/>
-    <col min="5" max="5" width="58.7272727272727" style="1" customWidth="1"/>
-    <col min="6" max="16383" width="8.72727272727273" style="1"/>
+    <col min="4" max="4" width="12.6333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="58.725" style="1" customWidth="1"/>
+    <col min="6" max="16383" width="8.725" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="4"/>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -7474,299 +8215,299 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="4"/>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="5"/>
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="4"/>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" ht="27" spans="1:7">
-      <c r="A4" s="4"/>
-      <c r="B4" s="3" t="s">
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" ht="25.5" spans="1:7">
+      <c r="A4" s="5"/>
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="4"/>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="5"/>
+      <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="4"/>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="5"/>
+      <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="4"/>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="5"/>
+      <c r="B7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="4"/>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="5"/>
+      <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" ht="27" spans="1:7">
-      <c r="A9" s="4"/>
-      <c r="B9" s="3" t="s">
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" ht="25.5" spans="1:7">
+      <c r="A9" s="5"/>
+      <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="4"/>
-      <c r="B10" s="3" t="s">
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" ht="14.25" spans="1:7">
+      <c r="A10" s="5"/>
+      <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="4"/>
-      <c r="B11" s="3" t="s">
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" ht="14.25" spans="1:7">
+      <c r="A11" s="5"/>
+      <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="3"/>
+      <c r="F11" s="2"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="4"/>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="5"/>
+      <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" ht="41.5" spans="1:7">
-      <c r="A13" s="4"/>
-      <c r="B13" s="3" t="s">
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" ht="28.5" spans="1:7">
+      <c r="A13" s="5"/>
+      <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" ht="27.5" spans="1:7">
-      <c r="A14" s="4"/>
-      <c r="B14" s="3" t="s">
+    <row r="14" ht="27" spans="1:7">
+      <c r="A14" s="5"/>
+      <c r="B14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="15" ht="28" spans="1:7">
-      <c r="A15" s="4"/>
-      <c r="B15" s="3" t="s">
+    <row r="15" ht="28.5" spans="1:7">
+      <c r="A15" s="5"/>
+      <c r="B15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="3"/>
+      <c r="F15" s="2"/>
       <c r="G15" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="4"/>
-      <c r="B16" s="3" t="s">
+    <row r="16" ht="14.25" spans="1:7">
+      <c r="A16" s="5"/>
+      <c r="B16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="4"/>
-      <c r="B17" s="3" t="s">
+    <row r="17" ht="14.25" spans="1:7">
+      <c r="A17" s="5"/>
+      <c r="B17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="18" ht="27.5" spans="1:7">
-      <c r="A18" s="4"/>
-      <c r="B18" s="3" t="s">
+    <row r="18" ht="27" spans="1:7">
+      <c r="A18" s="5"/>
+      <c r="B18" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -7774,1943 +8515,3616 @@
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="4"/>
-      <c r="B19" s="3" t="s">
+      <c r="A19" s="5"/>
+      <c r="B19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="2" t="s">
         <v>55</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="20" ht="41.5" spans="1:7">
-      <c r="A20" s="4"/>
-      <c r="B20" s="3" t="s">
+    <row r="20" ht="41.25" spans="1:7">
+      <c r="A20" s="5"/>
+      <c r="B20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="21" ht="28" spans="1:7">
-      <c r="A21" s="4"/>
-      <c r="B21" s="3" t="s">
+    <row r="21" ht="28.5" spans="1:7">
+      <c r="A21" s="5"/>
+      <c r="B21" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="22" ht="42" spans="1:7">
-      <c r="A22" s="4"/>
-      <c r="B22" s="3" t="s">
+    <row r="22" ht="42.75" spans="1:7">
+      <c r="A22" s="5"/>
+      <c r="B22" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="4"/>
-      <c r="B23" s="3" t="s">
+    <row r="23" ht="14.25" spans="1:7">
+      <c r="A23" s="5"/>
+      <c r="B23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="F23" s="3"/>
+      <c r="F23" s="2"/>
       <c r="G23" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="4"/>
-      <c r="B24" s="3" t="s">
+    <row r="24" ht="14.25" spans="1:7">
+      <c r="A24" s="5"/>
+      <c r="B24" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="3"/>
+      <c r="F24" s="2"/>
       <c r="G24" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="25" ht="27.5" spans="1:7">
-      <c r="A25" s="4"/>
-      <c r="B25" s="3" t="s">
+    <row r="25" ht="14.25" spans="1:7">
+      <c r="A25" s="5"/>
+      <c r="B25" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F25" s="3"/>
+      <c r="F25" s="2"/>
       <c r="G25" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="4"/>
-      <c r="B26" s="3" t="s">
+      <c r="A26" s="5"/>
+      <c r="B26" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="F26" s="3"/>
+      <c r="F26" s="2"/>
       <c r="G26" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="4"/>
-      <c r="B27" s="3" t="s">
+    <row r="27" ht="14.25" spans="1:7">
+      <c r="A27" s="5"/>
+      <c r="B27" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F27" s="3"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="4"/>
-      <c r="B28" s="3" t="s">
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" ht="14.25" spans="1:7">
+      <c r="A28" s="5"/>
+      <c r="B28" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="3"/>
+      <c r="F28" s="2"/>
       <c r="G28" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="4"/>
-      <c r="B29" s="3" t="s">
+    <row r="29" ht="14.25" spans="1:7">
+      <c r="A29" s="5"/>
+      <c r="B29" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F29" s="3"/>
+      <c r="F29" s="2"/>
       <c r="G29" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="30" ht="27" spans="1:7">
-      <c r="A30" s="4"/>
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="1:7">
+      <c r="A30" s="5"/>
+      <c r="B30" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="F30" s="3"/>
+      <c r="F30" s="2"/>
       <c r="G30" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="31" ht="27.5" spans="1:7">
-      <c r="A31" s="4"/>
-      <c r="B31" s="3" t="s">
+    <row r="31" ht="27" spans="1:7">
+      <c r="A31" s="5"/>
+      <c r="B31" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F31" s="3"/>
+      <c r="F31" s="2"/>
       <c r="G31" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="4"/>
-      <c r="B32" s="3" t="s">
+    <row r="32" ht="14.25" spans="1:7">
+      <c r="A32" s="5"/>
+      <c r="B32" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="F32" s="3"/>
+      <c r="F32" s="2"/>
       <c r="G32" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="4"/>
-      <c r="B33" s="3" t="s">
+    <row r="33" ht="14.25" spans="1:7">
+      <c r="A33" s="5"/>
+      <c r="B33" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="F33" s="3"/>
+      <c r="F33" s="2"/>
       <c r="G33" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="4"/>
-      <c r="B34" s="3" t="s">
+    <row r="34" ht="14.25" spans="1:7">
+      <c r="A34" s="5"/>
+      <c r="B34" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F34" s="3"/>
+      <c r="F34" s="2"/>
       <c r="G34" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" ht="28" spans="1:7">
-      <c r="A35" s="4"/>
-      <c r="B35" s="3" t="s">
+    <row r="35" ht="28.5" spans="1:7">
+      <c r="A35" s="5"/>
+      <c r="B35" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="2" t="s">
         <v>91</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="36" ht="55" spans="1:7">
-      <c r="A36" s="4"/>
-      <c r="B36" s="3" t="s">
+    <row r="36" ht="54" spans="1:7">
+      <c r="A36" s="5"/>
+      <c r="B36" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="2" t="s">
         <v>91</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="37" ht="28" spans="1:7">
-      <c r="A37" s="4"/>
-      <c r="B37" s="3" t="s">
+    <row r="37" ht="27" spans="1:7">
+      <c r="A37" s="5"/>
+      <c r="B37" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="2" t="s">
         <v>91</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="38" ht="27.5" spans="1:7">
-      <c r="A38" s="4"/>
-      <c r="B38" s="3" t="s">
+    <row r="38" ht="27" spans="1:7">
+      <c r="A38" s="5"/>
+      <c r="B38" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="2" t="s">
         <v>91</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="4"/>
-      <c r="B39" s="3" t="s">
+    <row r="39" ht="14.25" spans="1:7">
+      <c r="A39" s="5"/>
+      <c r="B39" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="F39" s="3"/>
+      <c r="F39" s="2"/>
       <c r="G39" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="4"/>
-      <c r="B40" s="3" t="s">
+    <row r="40" ht="14.25" spans="1:7">
+      <c r="A40" s="5"/>
+      <c r="B40" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="E40" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F40" s="3"/>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="4"/>
-      <c r="B41" s="3" t="s">
+      <c r="F40" s="2"/>
+    </row>
+    <row r="41" ht="14.25" spans="1:7">
+      <c r="A41" s="5"/>
+      <c r="B41" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="E41" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="F41" s="3"/>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="4"/>
-      <c r="B42" s="3" t="s">
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" ht="14.25" spans="1:7">
+      <c r="A42" s="5"/>
+      <c r="B42" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="F42" s="3"/>
+      <c r="F42" s="2"/>
       <c r="G42" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="4"/>
-      <c r="B43" s="3" t="s">
+    <row r="43" ht="14.25" spans="1:7">
+      <c r="A43" s="5"/>
+      <c r="B43" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="E43" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="F43" s="3"/>
+      <c r="F43" s="2"/>
       <c r="G43" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="4"/>
-      <c r="B44" s="3" t="s">
+    <row r="44" ht="14.25" spans="1:7">
+      <c r="A44" s="5"/>
+      <c r="B44" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="F44" s="3"/>
+      <c r="F44" s="2"/>
       <c r="G44" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="45" ht="42" spans="1:7">
-      <c r="A45" s="4"/>
-      <c r="B45" s="3" t="s">
+    <row r="45" ht="42.75" spans="1:7">
+      <c r="A45" s="5"/>
+      <c r="B45" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="E45" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="F45" s="3"/>
+      <c r="F45" s="2"/>
       <c r="G45" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="4"/>
-      <c r="B46" s="3" t="s">
+    <row r="46" ht="14.25" spans="1:7">
+      <c r="A46" s="5"/>
+      <c r="B46" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="E46" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F46" s="3"/>
+      <c r="F46" s="2"/>
       <c r="G46" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="47" ht="28" spans="1:7">
-      <c r="A47" s="4"/>
-      <c r="B47" s="3" t="s">
+    <row r="47" ht="28.5" spans="1:7">
+      <c r="A47" s="5"/>
+      <c r="B47" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="E47" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="F47" s="3"/>
+      <c r="F47" s="2"/>
       <c r="G47" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="4"/>
-      <c r="B48" s="3" t="s">
+    <row r="48" ht="14.25" spans="1:7">
+      <c r="A48" s="5"/>
+      <c r="B48" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="E48" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="F48" s="3"/>
+      <c r="F48" s="2"/>
       <c r="G48" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="4"/>
-      <c r="B49" s="3" t="s">
+    <row r="49" ht="14.25" spans="1:7">
+      <c r="A49" s="5"/>
+      <c r="B49" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="E49" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="F49" s="3"/>
+      <c r="F49" s="2"/>
       <c r="G49" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="4"/>
-      <c r="B50" s="3" t="s">
+    <row r="50" ht="14.25" spans="1:7">
+      <c r="A50" s="5"/>
+      <c r="B50" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D50" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="E50" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F50" s="3"/>
+      <c r="F50" s="2"/>
       <c r="G50" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="51" ht="27" spans="1:7">
-      <c r="A51" s="4"/>
-      <c r="B51" s="3" t="s">
+    <row r="51" ht="25.5" spans="1:7">
+      <c r="A51" s="5"/>
+      <c r="B51" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="E51" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F51" s="3"/>
+      <c r="F51" s="2"/>
       <c r="G51" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="52" ht="27.5" spans="1:7">
-      <c r="A52" s="4"/>
-      <c r="B52" s="3" t="s">
+    <row r="52" ht="14.25" spans="1:7">
+      <c r="A52" s="5"/>
+      <c r="B52" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="E52" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="F52" s="3"/>
+      <c r="F52" s="2"/>
       <c r="G52" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="4"/>
-      <c r="B53" s="3" t="s">
+    <row r="53" ht="14.25" spans="1:7">
+      <c r="A53" s="5"/>
+      <c r="B53" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E53" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="F53" s="3"/>
+      <c r="F53" s="2"/>
       <c r="G53" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="4"/>
-      <c r="B54" s="3" t="s">
+      <c r="A54" s="5"/>
+      <c r="B54" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D54" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="E54" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="F54" s="3"/>
+      <c r="F54" s="2"/>
       <c r="G54" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="4"/>
-      <c r="B55" s="3" t="s">
+    <row r="55" ht="14.25" spans="1:7">
+      <c r="A55" s="5"/>
+      <c r="B55" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="E55" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="F55" s="3"/>
+      <c r="F55" s="2"/>
       <c r="G55" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="4"/>
-      <c r="B56" s="3" t="s">
+    <row r="56" ht="14.25" spans="1:7">
+      <c r="A56" s="5"/>
+      <c r="B56" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D56" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="E56" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F56" s="3"/>
+      <c r="F56" s="2"/>
       <c r="G56" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="4"/>
-      <c r="B57" s="3" t="s">
+      <c r="A57" s="5"/>
+      <c r="B57" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="E57" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="F57" s="3"/>
+      <c r="F57" s="2"/>
       <c r="G57" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="4"/>
-      <c r="B58" s="3" t="s">
+      <c r="A58" s="5"/>
+      <c r="B58" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E58" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="F58" s="3"/>
+      <c r="F58" s="2"/>
       <c r="G58" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="4"/>
-      <c r="B59" s="3" t="s">
+      <c r="A59" s="5"/>
+      <c r="B59" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="E59" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="F59" s="3"/>
+      <c r="F59" s="2"/>
       <c r="G59" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="60" ht="27" spans="1:7">
-      <c r="A60" s="4"/>
-      <c r="B60" s="3" t="s">
+    <row r="60" ht="25.5" spans="1:7">
+      <c r="A60" s="5"/>
+      <c r="B60" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D60" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="E60" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="F60" s="3"/>
+      <c r="F60" s="2"/>
       <c r="G60" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="4"/>
-      <c r="B61" s="3" t="s">
+    <row r="61" ht="14.25" spans="1:7">
+      <c r="A61" s="5"/>
+      <c r="B61" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="D61" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="E61" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F61" s="3"/>
-    </row>
-    <row r="62" ht="28" spans="1:7">
-      <c r="A62" s="4"/>
-      <c r="B62" s="3" t="s">
+      <c r="F61" s="2"/>
+    </row>
+    <row r="62" ht="27" spans="1:7">
+      <c r="A62" s="5"/>
+      <c r="B62" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D62" s="3" t="s">
+      <c r="D62" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="E62" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="F62" s="3"/>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="4"/>
-      <c r="B63" s="3" t="s">
+      <c r="F62" s="2"/>
+    </row>
+    <row r="63" ht="14.25" spans="1:7">
+      <c r="A63" s="5"/>
+      <c r="B63" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="E63" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="F63" s="3"/>
+      <c r="F63" s="2"/>
       <c r="G63" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="4"/>
-      <c r="B64" s="3" t="s">
+    <row r="64" ht="14.25" spans="1:7">
+      <c r="A64" s="5"/>
+      <c r="B64" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D64" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="E64" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="F64" s="3"/>
+      <c r="F64" s="2"/>
       <c r="G64" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="65" ht="27.5" spans="1:7">
-      <c r="A65" s="4"/>
-      <c r="B65" s="3" t="s">
+    <row r="65" ht="27" spans="1:7">
+      <c r="A65" s="5"/>
+      <c r="B65" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D65" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="E65" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="66" ht="28" spans="1:7">
-      <c r="A66" s="4"/>
-      <c r="B66" s="3" t="s">
+    <row r="66" ht="27" spans="1:7">
+      <c r="A66" s="5"/>
+      <c r="B66" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="D66" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="E66" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="F66" s="3"/>
+      <c r="F66" s="2"/>
       <c r="G66" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="4"/>
-      <c r="B67" s="3" t="s">
+    <row r="67" ht="14.25" spans="1:7">
+      <c r="A67" s="5"/>
+      <c r="B67" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="E67" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="F67" s="3"/>
+      <c r="F67" s="2"/>
       <c r="G67" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="68" ht="41.5" spans="1:7">
-      <c r="A68" s="4"/>
-      <c r="B68" s="3" t="s">
+    <row r="68" ht="41.25" spans="1:7">
+      <c r="A68" s="5"/>
+      <c r="B68" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E68" s="5" t="s">
+      <c r="E68" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="F68" s="3"/>
+      <c r="F68" s="2"/>
       <c r="G68" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="69" ht="27.5" spans="1:7">
-      <c r="A69" s="4"/>
-      <c r="B69" s="3" t="s">
+    <row r="69" ht="27" spans="1:7">
+      <c r="A69" s="5"/>
+      <c r="B69" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="E69" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="F69" s="3"/>
+      <c r="F69" s="2"/>
       <c r="G69" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="70" ht="27.5" spans="1:7">
-      <c r="A70" s="4"/>
-      <c r="B70" s="3" t="s">
+    <row r="70" ht="27" spans="1:7">
+      <c r="A70" s="5"/>
+      <c r="B70" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E70" s="5" t="s">
+      <c r="E70" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="F70" s="3"/>
+      <c r="F70" s="2"/>
       <c r="G70" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="4"/>
-      <c r="B71" s="3" t="s">
+    <row r="71" ht="14.25" spans="1:7">
+      <c r="A71" s="5"/>
+      <c r="B71" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="E71" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="F71" s="3"/>
+      <c r="F71" s="2"/>
       <c r="G71" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
-      <c r="A72" s="4"/>
-      <c r="B72" s="3" t="s">
+    <row r="72" ht="14.25" spans="1:7">
+      <c r="A72" s="5"/>
+      <c r="B72" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="E72" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="F72" s="3"/>
+      <c r="F72" s="2"/>
       <c r="G72" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="73" ht="56" spans="1:7">
-      <c r="A73" s="4"/>
-      <c r="B73" s="3" t="s">
+    <row r="73" ht="57" spans="1:7">
+      <c r="A73" s="5"/>
+      <c r="B73" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="E73" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="F73" s="3"/>
+      <c r="F73" s="2"/>
       <c r="G73" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="74" ht="41.5" spans="1:7">
-      <c r="A74" s="4"/>
-      <c r="B74" s="3" t="s">
+    <row r="74" ht="41.25" spans="1:7">
+      <c r="A74" s="5"/>
+      <c r="B74" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="E74" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="F74" s="3"/>
+      <c r="F74" s="2"/>
       <c r="G74" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="4"/>
-      <c r="B75" s="3" t="s">
+      <c r="A75" s="5"/>
+      <c r="B75" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E75" s="5" t="s">
+      <c r="E75" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="F75" s="3"/>
+      <c r="F75" s="2"/>
       <c r="G75" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
-      <c r="A76" s="4"/>
-      <c r="B76" s="3" t="s">
+    <row r="76" ht="14.25" spans="1:7">
+      <c r="A76" s="5"/>
+      <c r="B76" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D76" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E76" s="5" t="s">
+      <c r="E76" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="F76" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="4"/>
-      <c r="B77" s="3" t="s">
+    <row r="77" ht="14.25" spans="1:7">
+      <c r="A77" s="5"/>
+      <c r="B77" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E77" s="5" t="s">
+      <c r="E77" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="F77" s="3"/>
-    </row>
-    <row r="78" ht="41.5" spans="1:7">
-      <c r="A78" s="4"/>
-      <c r="B78" s="3" t="s">
+      <c r="F77" s="2"/>
+    </row>
+    <row r="78" ht="39.75" spans="1:7">
+      <c r="A78" s="5"/>
+      <c r="B78" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E78" s="5" t="s">
+      <c r="E78" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="F78" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="79" ht="28" spans="1:7">
-      <c r="A79" s="4"/>
-      <c r="B79" s="3" t="s">
+    <row r="79" ht="28.5" spans="1:7">
+      <c r="A79" s="5"/>
+      <c r="B79" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E79" s="5" t="s">
+      <c r="E79" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="F79" s="2" t="s">
         <v>37</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
-      <c r="A80" s="4"/>
-      <c r="B80" s="3" t="s">
+    <row r="80" ht="14.25" spans="1:7">
+      <c r="A80" s="5"/>
+      <c r="B80" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E80" s="5" t="s">
+      <c r="E80" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F80" s="3"/>
+      <c r="F80" s="2"/>
       <c r="G80" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="81" ht="28" spans="1:7">
-      <c r="A81" s="4"/>
-      <c r="B81" s="3" t="s">
+    <row r="81" ht="28.5" spans="1:7">
+      <c r="A81" s="5"/>
+      <c r="B81" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E81" s="5" t="s">
+      <c r="E81" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="F81" s="3"/>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82" s="4"/>
-      <c r="B82" s="3" t="s">
+      <c r="F81" s="2"/>
+    </row>
+    <row r="82" ht="14.25" spans="1:7">
+      <c r="A82" s="5"/>
+      <c r="B82" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E82" s="5" t="s">
+      <c r="E82" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="F82" s="3"/>
-    </row>
-    <row r="83" ht="27.5" spans="1:7">
-      <c r="A83" s="4"/>
-      <c r="B83" s="3" t="s">
+      <c r="F82" s="2"/>
+    </row>
+    <row r="83" ht="14.25" spans="1:7">
+      <c r="A83" s="5"/>
+      <c r="B83" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E83" s="5" t="s">
+      <c r="E83" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F83" s="3"/>
-    </row>
-    <row r="84" ht="28" spans="1:7">
-      <c r="A84" s="4"/>
-      <c r="B84" s="3" t="s">
+      <c r="F83" s="2"/>
+    </row>
+    <row r="84" ht="28.5" spans="1:7">
+      <c r="A84" s="5"/>
+      <c r="B84" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E84" s="5" t="s">
+      <c r="E84" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="F84" s="3"/>
-    </row>
-    <row r="85" ht="55" spans="1:7">
-      <c r="A85" s="4"/>
-      <c r="B85" s="3" t="s">
+      <c r="F84" s="2"/>
+    </row>
+    <row r="85" ht="41.25" spans="1:7">
+      <c r="A85" s="5"/>
+      <c r="B85" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E85" s="5" t="s">
+      <c r="E85" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="F85" s="3"/>
-    </row>
-    <row r="86" spans="1:7">
-      <c r="A86" s="4"/>
-      <c r="B86" s="3" t="s">
+      <c r="F85" s="2"/>
+    </row>
+    <row r="86" ht="14.25" spans="1:7">
+      <c r="A86" s="5"/>
+      <c r="B86" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C86" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="D86" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="5" t="s">
+      <c r="E86" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="F86" s="3"/>
-    </row>
-    <row r="87" spans="1:7">
-      <c r="A87" s="4"/>
-      <c r="B87" s="3" t="s">
+      <c r="F86" s="2"/>
+    </row>
+    <row r="87" ht="14.25" spans="1:7">
+      <c r="A87" s="5"/>
+      <c r="B87" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E87" s="5" t="s">
+      <c r="E87" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F87" s="3"/>
-    </row>
-    <row r="88" ht="28" spans="1:7">
-      <c r="A88" s="4"/>
-      <c r="B88" s="3" t="s">
+      <c r="F87" s="2"/>
+    </row>
+    <row r="88" ht="28.5" spans="1:7">
+      <c r="A88" s="5"/>
+      <c r="B88" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C88" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="D88" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E88" s="5" t="s">
+      <c r="E88" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="F88" s="3"/>
+      <c r="F88" s="2"/>
       <c r="G88" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="89" ht="56" spans="1:7">
-      <c r="A89" s="4"/>
-      <c r="B89" s="3" t="s">
+    <row r="89" ht="55.5" spans="1:7">
+      <c r="A89" s="5"/>
+      <c r="B89" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C89" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D89" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E89" s="5" t="s">
+      <c r="E89" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="F89" s="3"/>
+      <c r="F89" s="2"/>
       <c r="G89" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="90" ht="28" spans="1:7">
-      <c r="A90" s="4"/>
-      <c r="B90" s="3" t="s">
+    <row r="90" ht="28.5" spans="1:7">
+      <c r="A90" s="5"/>
+      <c r="B90" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C90" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="D90" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E90" s="5" t="s">
+      <c r="E90" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="F90" s="3"/>
+      <c r="F90" s="2"/>
       <c r="G90" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="91" spans="1:7">
-      <c r="A91" s="4"/>
-      <c r="B91" s="3" t="s">
+      <c r="A91" s="5"/>
+      <c r="B91" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C91" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="5" t="s">
+      <c r="E91" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="F91" s="3"/>
+      <c r="F91" s="2"/>
       <c r="G91" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
-      <c r="A92" s="4"/>
-      <c r="B92" s="3" t="s">
+    <row r="92" ht="14.25" spans="1:7">
+      <c r="A92" s="5"/>
+      <c r="B92" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C92" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="D92" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E92" s="5" t="s">
+      <c r="E92" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="F92" s="3"/>
+      <c r="F92" s="2"/>
       <c r="G92" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="93" ht="41.5" spans="1:7">
-      <c r="A93" s="4"/>
-      <c r="B93" s="3" t="s">
+    <row r="93" ht="28.5" spans="1:7">
+      <c r="A93" s="5"/>
+      <c r="B93" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D93" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E93" s="5" t="s">
+      <c r="E93" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="F93" s="3"/>
+      <c r="F93" s="2"/>
       <c r="G93" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="94" ht="27.5" spans="1:7">
-      <c r="A94" s="4"/>
-      <c r="B94" s="3" t="s">
+    <row r="94" ht="27" spans="1:7">
+      <c r="A94" s="5"/>
+      <c r="B94" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E94" s="5" t="s">
+      <c r="E94" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="F94" s="3"/>
+      <c r="F94" s="2"/>
       <c r="G94" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
-      <c r="A95" s="4"/>
-      <c r="B95" s="3" t="s">
+    <row r="95" ht="14.25" spans="1:7">
+      <c r="A95" s="5"/>
+      <c r="B95" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="D95" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E95" s="5" t="s">
+      <c r="E95" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="F95" s="3"/>
+      <c r="F95" s="2"/>
       <c r="G95" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
-      <c r="A96" s="4"/>
-      <c r="B96" s="3" t="s">
+    <row r="96" ht="14.25" spans="1:7">
+      <c r="A96" s="5"/>
+      <c r="B96" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C96" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E96" s="5" t="s">
+      <c r="E96" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="F96" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
-      <c r="A97" s="4"/>
-      <c r="B97" s="3" t="s">
+    <row r="97" ht="14.25" spans="1:7">
+      <c r="A97" s="5"/>
+      <c r="B97" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D97" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E97" s="5" t="s">
+      <c r="E97" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="F97" s="3" t="s">
+      <c r="F97" s="2" t="s">
         <v>41</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="98" ht="28" spans="1:7">
-      <c r="A98" s="4"/>
-      <c r="B98" s="3" t="s">
+    <row r="98" ht="28.5" spans="1:7">
+      <c r="A98" s="5"/>
+      <c r="B98" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D98" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E98" s="5" t="s">
+      <c r="E98" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="F98" s="3"/>
+      <c r="F98" s="2"/>
       <c r="G98" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
-      <c r="A99" s="4"/>
-      <c r="B99" s="3" t="s">
+    <row r="99" ht="14.25" spans="1:7">
+      <c r="A99" s="5"/>
+      <c r="B99" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C99" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="D99" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E99" s="5" t="s">
+      <c r="E99" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="F99" s="3"/>
+      <c r="F99" s="2"/>
       <c r="G99" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
-      <c r="A100" s="4"/>
-      <c r="B100" s="3" t="s">
+    <row r="100" ht="14.25" spans="1:7">
+      <c r="A100" s="5"/>
+      <c r="B100" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C100" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E100" s="5" t="s">
+      <c r="E100" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="F100" s="3"/>
+      <c r="F100" s="2"/>
       <c r="G100" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
-      <c r="A101" s="4"/>
-      <c r="B101" s="3" t="s">
+    <row r="101" ht="14.25" spans="1:7">
+      <c r="A101" s="5"/>
+      <c r="B101" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="C101" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E101" s="5" t="s">
+      <c r="E101" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="F101" s="3"/>
+      <c r="F101" s="2"/>
       <c r="G101" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="102" ht="27.5" spans="1:7">
-      <c r="A102" s="4"/>
-      <c r="B102" s="3" t="s">
+    <row r="102" ht="14.25" spans="1:7">
+      <c r="A102" s="5"/>
+      <c r="B102" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="C102" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D102" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E102" s="5" t="s">
+      <c r="E102" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F102" s="3"/>
+      <c r="F102" s="2"/>
       <c r="G102" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
-      <c r="A103" s="4"/>
-      <c r="B103" s="3" t="s">
+    <row r="103" ht="14.25" spans="1:7">
+      <c r="A103" s="5"/>
+      <c r="B103" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C103" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D103" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E103" s="5" t="s">
+      <c r="E103" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="F103" s="3"/>
+      <c r="F103" s="2"/>
       <c r="G103" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
-      <c r="A104" s="4"/>
-      <c r="B104" s="3" t="s">
+    <row r="104" ht="14.25" spans="1:7">
+      <c r="A104" s="5"/>
+      <c r="B104" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="C104" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D104" s="3" t="s">
+      <c r="D104" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E104" s="5" t="s">
+      <c r="E104" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="F104" s="3"/>
+      <c r="F104" s="2"/>
       <c r="G104" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
-      <c r="A105" s="4"/>
-      <c r="B105" s="3" t="s">
+    <row r="105" ht="14.25" spans="1:7">
+      <c r="A105" s="5"/>
+      <c r="B105" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C105" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D105" s="3" t="s">
+      <c r="D105" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E105" s="5" t="s">
+      <c r="E105" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="F105" s="3"/>
+      <c r="F105" s="2"/>
       <c r="G105" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="106" spans="1:7">
-      <c r="A106" s="4"/>
-      <c r="B106" s="3" t="s">
+      <c r="A106" s="5"/>
+      <c r="B106" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C106" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="D106" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E106" s="5" t="s">
+      <c r="E106" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="F106" s="3"/>
+      <c r="F106" s="2"/>
       <c r="G106" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
-      <c r="A107" s="4"/>
-      <c r="B107" s="3" t="s">
+    <row r="107" ht="14.25" spans="1:7">
+      <c r="A107" s="5"/>
+      <c r="B107" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C107" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D107" s="3" t="s">
+      <c r="D107" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E107" s="5" t="s">
+      <c r="E107" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="F107" s="3" t="s">
+      <c r="F107" s="2" t="s">
         <v>91</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="108" ht="28" spans="1:7">
-      <c r="A108" s="4"/>
-      <c r="B108" s="3" t="s">
+    <row r="108" ht="28.5" spans="1:7">
+      <c r="A108" s="5"/>
+      <c r="B108" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="C108" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D108" s="3" t="s">
+      <c r="D108" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E108" s="5" t="s">
+      <c r="E108" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="F108" s="3"/>
+      <c r="F108" s="2"/>
       <c r="G108" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="109" ht="28" spans="1:7">
-      <c r="A109" s="4"/>
-      <c r="B109" s="3" t="s">
+    <row r="109" ht="28.5" spans="1:7">
+      <c r="A109" s="5"/>
+      <c r="B109" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="C109" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D109" s="3" t="s">
+      <c r="D109" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E109" s="5" t="s">
+      <c r="E109" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="F109" s="3"/>
+      <c r="F109" s="2"/>
       <c r="G109" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
-      <c r="A110" s="4"/>
-      <c r="B110" s="3" t="s">
+    <row r="110" ht="14.25" spans="1:7">
+      <c r="A110" s="5"/>
+      <c r="B110" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="C110" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D110" s="3" t="s">
+      <c r="D110" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E110" s="5" t="s">
+      <c r="E110" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="F110" s="3" t="s">
+      <c r="F110" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="111" ht="56" spans="1:7">
-      <c r="A111" s="4"/>
-      <c r="B111" s="3" t="s">
+    <row r="111" ht="55.5" spans="1:7">
+      <c r="A111" s="5"/>
+      <c r="B111" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C111" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D111" s="3" t="s">
+      <c r="D111" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E111" s="5" t="s">
+      <c r="E111" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="F111" s="3"/>
+      <c r="F111" s="2"/>
       <c r="G111" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="112" ht="28" spans="1:7">
-      <c r="A112" s="4"/>
-      <c r="B112" s="3" t="s">
+    <row r="112" ht="27" spans="1:7">
+      <c r="A112" s="5"/>
+      <c r="B112" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="C112" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D112" s="3" t="s">
+      <c r="D112" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E112" s="5" t="s">
+      <c r="E112" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="F112" s="3"/>
+      <c r="F112" s="2"/>
       <c r="G112" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
-      <c r="A113" s="4"/>
-      <c r="B113" s="3" t="s">
+    <row r="113" ht="14.25" spans="1:7">
+      <c r="A113" s="5"/>
+      <c r="B113" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="C113" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D113" s="3" t="s">
+      <c r="D113" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E113" s="5" t="s">
+      <c r="E113" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="F113" s="3"/>
+      <c r="F113" s="2"/>
       <c r="G113" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
-      <c r="A114" s="4"/>
-      <c r="B114" s="3" t="s">
+    <row r="114" ht="14.25" spans="1:7">
+      <c r="A114" s="5"/>
+      <c r="B114" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="C114" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="D114" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E114" s="5" t="s">
+      <c r="E114" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="F114" s="3"/>
+      <c r="F114" s="2"/>
       <c r="G114" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="115" ht="27.5" spans="1:7">
-      <c r="A115" s="4"/>
-      <c r="B115" s="3" t="s">
+    <row r="115" ht="27" spans="1:7">
+      <c r="A115" s="5"/>
+      <c r="B115" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="C115" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D115" s="3" t="s">
+      <c r="D115" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E115" s="5" t="s">
+      <c r="E115" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="F115" s="3"/>
+      <c r="F115" s="2"/>
       <c r="G115" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="116" ht="27.5" spans="1:7">
-      <c r="A116" s="4"/>
-      <c r="B116" s="3" t="s">
+    <row r="116" ht="28.5" spans="1:7">
+      <c r="A116" s="5"/>
+      <c r="B116" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="C116" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D116" s="3" t="s">
+      <c r="D116" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="E116" s="5" t="s">
+      <c r="E116" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="F116" s="3"/>
+      <c r="F116" s="2"/>
       <c r="G116" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="117" ht="27.5" spans="1:7">
-      <c r="A117" s="4"/>
-      <c r="B117" s="3" t="s">
+    <row r="117" ht="27" spans="1:7">
+      <c r="A117" s="5"/>
+      <c r="B117" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="C117" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D117" s="3" t="s">
+      <c r="D117" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="E117" s="5" t="s">
+      <c r="E117" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="F117" s="3"/>
+      <c r="F117" s="2"/>
       <c r="G117" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="118" ht="28" spans="1:7">
-      <c r="A118" s="4"/>
-      <c r="B118" s="3" t="s">
+    <row r="118" ht="28.5" spans="1:7">
+      <c r="A118" s="5"/>
+      <c r="B118" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="C118" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D118" s="3" t="s">
+      <c r="D118" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E118" s="5" t="s">
+      <c r="E118" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="F118" s="3" t="s">
+      <c r="F118" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="119" ht="27.5" spans="1:7">
-      <c r="A119" s="4"/>
-      <c r="B119" s="3" t="s">
+    <row r="119" ht="27" spans="1:7">
+      <c r="A119" s="5"/>
+      <c r="B119" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="C119" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D119" s="3" t="s">
+      <c r="D119" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E119" s="5" t="s">
+      <c r="E119" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="F119" s="3" t="s">
+      <c r="F119" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
-      <c r="A120" s="4"/>
-      <c r="B120" s="3" t="s">
+    <row r="120" ht="14.25" spans="1:7">
+      <c r="A120" s="5"/>
+      <c r="B120" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C120" s="3" t="s">
+      <c r="C120" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D120" s="3" t="s">
+      <c r="D120" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E120" s="5" t="s">
+      <c r="E120" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="F120" s="3"/>
+      <c r="F120" s="2"/>
       <c r="G120" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="121" ht="28" spans="1:7">
-      <c r="A121" s="4"/>
-      <c r="B121" s="3" t="s">
+    <row r="121" spans="1:7">
+      <c r="A121" s="5"/>
+      <c r="B121" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="C121" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D121" s="3" t="s">
+      <c r="D121" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E121" s="3" t="s">
+      <c r="E121" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="F121" s="3"/>
+      <c r="F121" s="2"/>
       <c r="G121" s="1" t="s">
         <v>46</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I73"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="4.725" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="24.1833333333333" customWidth="1"/>
+    <col min="4" max="4" width="10.1833333333333" customWidth="1"/>
+    <col min="5" max="5" width="68.1833333333333" customWidth="1"/>
+    <col min="6" max="6" width="11.6333333333333" customWidth="1"/>
+    <col min="7" max="7" width="16.6333333333333" customWidth="1"/>
+    <col min="8" max="8" width="20.0916666666667" customWidth="1"/>
+    <col min="9" max="9" width="8.725" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F1" t="s">
+        <v>276</v>
+      </c>
+      <c r="G1" t="s">
+        <v>277</v>
+      </c>
+      <c r="H1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="2" ht="27" spans="1:9">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" ht="27" spans="1:9">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" ht="40.5" spans="1:9">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="10" ht="27" spans="1:9">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" ht="27" spans="1:9">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" ht="27" spans="1:8">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" ht="27" spans="1:8">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" ht="27" spans="1:8">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" ht="27" spans="1:8">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" ht="27" spans="1:8">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" ht="27" spans="1:8">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" ht="27" spans="1:8">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" ht="27" spans="1:8">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" ht="27" spans="1:8">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" ht="27" spans="1:8">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" ht="27" spans="1:8">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" ht="27" spans="1:8">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" ht="40.5" spans="1:8">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" ht="27" spans="1:8">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H48" s="2"/>
+    </row>
+    <row r="49" ht="27" spans="1:9">
+      <c r="A49" s="2">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="2">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H51" s="2"/>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="2">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H54" s="2"/>
+    </row>
+    <row r="55" ht="27" spans="1:9">
+      <c r="A55" s="2">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H56" s="2"/>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="2">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="2">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+    </row>
+    <row r="61" ht="40.5" spans="1:9">
+      <c r="A61" s="2">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H61" s="2"/>
+      <c r="I61" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="62" ht="27" spans="1:9">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="H62" s="2"/>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H63" s="2"/>
+    </row>
+    <row r="64" ht="27" spans="1:9">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="66" ht="27" spans="1:8">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="2">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="2">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="2">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="2">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="2">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="2">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H72" s="2"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="2">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H73" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
